--- a/public/templates/customer_import_template.xlsx
+++ b/public/templates/customer_import_template.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\code\bumdes\public\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7162A757-66D5-4E5B-964C-182F95DC3BB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66772CB6-BFA9-4357-A1C0-0B783872DD82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8E2EFA7C-69A2-4FF1-9320-3668AB5661C8}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>customer_id</t>
   </si>
@@ -54,13 +54,31 @@
     <t>due</t>
   </si>
   <si>
-    <t>site_id</t>
-  </si>
-  <si>
-    <t>package_id</t>
-  </si>
-  <si>
-    <t>device_id</t>
+    <t>latitude</t>
+  </si>
+  <si>
+    <t>longitude</t>
+  </si>
+  <si>
+    <t>site_code</t>
+  </si>
+  <si>
+    <t>package_code</t>
+  </si>
+  <si>
+    <t>device_code</t>
+  </si>
+  <si>
+    <t>serial_number</t>
+  </si>
+  <si>
+    <t>mac_address</t>
+  </si>
+  <si>
+    <t>due_reminder_days</t>
+  </si>
+  <si>
+    <t>grace_period</t>
   </si>
 </sst>
 </file>
@@ -96,8 +114,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -412,21 +431,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E9B4C7E-2D42-4AB0-9483-993CA7A668B5}">
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:O1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="31.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="25.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="3" width="20.7109375" customWidth="1"/>
+    <col min="4" max="15" width="20.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -436,23 +448,41 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="M1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
